--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124474161</v>
+        <v>124474168</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698368</v>
+        <v>698409</v>
       </c>
       <c r="R2" t="n">
-        <v>6646487</v>
+        <v>6646641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124462736</v>
+        <v>124474165</v>
       </c>
       <c r="B3" t="n">
-        <v>110163</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698509</v>
+        <v>698508</v>
       </c>
       <c r="R3" t="n">
-        <v>6646485</v>
+        <v>6646430</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124462750</v>
+        <v>124457969</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>98124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698509</v>
+        <v>698343</v>
       </c>
       <c r="R4" t="n">
-        <v>6646485</v>
+        <v>6646433</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124461033</v>
+        <v>124462473</v>
       </c>
       <c r="B5" t="n">
-        <v>103528</v>
+        <v>5176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698451</v>
+        <v>698461</v>
       </c>
       <c r="R5" t="n">
-        <v>6646709</v>
+        <v>6646553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124457542</v>
+        <v>124474156</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,38 +1202,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698344</v>
+        <v>698340</v>
       </c>
       <c r="R7" t="n">
-        <v>6646454</v>
+        <v>6646487</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,22 +1284,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124459075</v>
+        <v>124458289</v>
       </c>
       <c r="B8" t="n">
-        <v>30115</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,32 +1308,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>200985</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1337,13 +1348,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698467</v>
+        <v>698368</v>
       </c>
       <c r="R8" t="n">
-        <v>6646525</v>
+        <v>6646466</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124474162</v>
+        <v>124462750</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,45 +1423,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698476</v>
+        <v>698509</v>
       </c>
       <c r="R9" t="n">
-        <v>6646591</v>
+        <v>6646485</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,29 +1495,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124474166</v>
+        <v>124461033</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>103528</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,34 +1529,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698449</v>
+        <v>698451</v>
       </c>
       <c r="R10" t="n">
-        <v>6646765</v>
+        <v>6646709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,22 +1603,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474168</v>
+        <v>124457352</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,37 +1631,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698409</v>
+        <v>698343</v>
       </c>
       <c r="R11" t="n">
-        <v>6646641</v>
+        <v>6646433</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,22 +1705,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124457352</v>
+        <v>124474161</v>
       </c>
       <c r="B12" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,41 +1729,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698343</v>
+        <v>698368</v>
       </c>
       <c r="R12" t="n">
-        <v>6646433</v>
+        <v>6646487</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,28 +1805,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124457802</v>
+        <v>124459239</v>
       </c>
       <c r="B13" t="n">
-        <v>5196</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,41 +1836,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698365</v>
+        <v>698474</v>
       </c>
       <c r="R13" t="n">
-        <v>6646448</v>
+        <v>6646510</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124459239</v>
+        <v>124457671</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,50 +1947,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698474</v>
+        <v>698365</v>
       </c>
       <c r="R14" t="n">
-        <v>6646510</v>
+        <v>6646448</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124458289</v>
+        <v>124462497</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,53 +2049,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698368</v>
+        <v>698461</v>
       </c>
       <c r="R15" t="n">
-        <v>6646466</v>
+        <v>6646553</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2122,7 +2121,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2141,7 +2139,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124474163</v>
+        <v>124474162</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2176,7 +2174,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2185,7 +2183,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698473</v>
+        <v>698476</v>
       </c>
       <c r="R16" t="n">
         <v>6646591</v>
@@ -2248,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462473</v>
+        <v>124457802</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2264,39 +2262,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698461</v>
+        <v>698365</v>
       </c>
       <c r="R17" t="n">
-        <v>6646553</v>
+        <v>6646448</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124457484</v>
+        <v>124474163</v>
       </c>
       <c r="B18" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2367,38 +2360,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698344</v>
+        <v>698473</v>
       </c>
       <c r="R18" t="n">
-        <v>6646454</v>
+        <v>6646591</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,28 +2436,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124457671</v>
+        <v>124457484</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>105117</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,25 +2467,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2497,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698365</v>
+        <v>698344</v>
       </c>
       <c r="R19" t="n">
-        <v>6646448</v>
+        <v>6646454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124474164</v>
+        <v>124474166</v>
       </c>
       <c r="B20" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2575,21 +2573,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2599,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698354</v>
+        <v>698449</v>
       </c>
       <c r="R20" t="n">
-        <v>6646460</v>
+        <v>6646765</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124457969</v>
+        <v>124462736</v>
       </c>
       <c r="B21" t="n">
-        <v>98124</v>
+        <v>110163</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,34 +2675,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698343</v>
+        <v>698509</v>
       </c>
       <c r="R21" t="n">
-        <v>6646433</v>
+        <v>6646485</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2763,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124474165</v>
+        <v>124459075</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>30115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,34 +2777,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698508</v>
+        <v>698467</v>
       </c>
       <c r="R22" t="n">
-        <v>6646430</v>
+        <v>6646525</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,28 +2850,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462497</v>
+        <v>124474164</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2881,34 +2885,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698461</v>
+        <v>698354</v>
       </c>
       <c r="R23" t="n">
-        <v>6646553</v>
+        <v>6646460</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2955,22 +2959,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124474156</v>
+        <v>124457542</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2979,42 +2983,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698340</v>
+        <v>698344</v>
       </c>
       <c r="R24" t="n">
-        <v>6646487</v>
+        <v>6646454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124474168</v>
+        <v>124462497</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698409</v>
+        <v>698461</v>
       </c>
       <c r="R2" t="n">
-        <v>6646641</v>
+        <v>6646553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124474165</v>
+        <v>124457678</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698508</v>
+        <v>698365</v>
       </c>
       <c r="R3" t="n">
-        <v>6646430</v>
+        <v>6646448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124457969</v>
+        <v>124474163</v>
       </c>
       <c r="B4" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698343</v>
+        <v>698473</v>
       </c>
       <c r="R4" t="n">
-        <v>6646433</v>
+        <v>6646591</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,28 +967,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124462473</v>
+        <v>124474162</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +998,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698461</v>
+        <v>698476</v>
       </c>
       <c r="R5" t="n">
-        <v>6646553</v>
+        <v>6646591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,28 +1074,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124457678</v>
+        <v>124458289</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1105,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698365</v>
+        <v>698368</v>
       </c>
       <c r="R6" t="n">
-        <v>6646448</v>
+        <v>6646466</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,6 +1189,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124474156</v>
+        <v>124457969</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,45 +1220,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698340</v>
+        <v>698343</v>
       </c>
       <c r="R7" t="n">
-        <v>6646487</v>
+        <v>6646433</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,22 +1298,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124458289</v>
+        <v>124457352</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,50 +1322,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698368</v>
+        <v>698343</v>
       </c>
       <c r="R8" t="n">
-        <v>6646466</v>
+        <v>6646433</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,7 +1394,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1411,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124462750</v>
+        <v>124474164</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,37 +1428,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698509</v>
+        <v>698354</v>
       </c>
       <c r="R9" t="n">
-        <v>6646485</v>
+        <v>6646460</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,22 +1502,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124461033</v>
+        <v>124462473</v>
       </c>
       <c r="B10" t="n">
-        <v>103528</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,34 +1530,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698451</v>
+        <v>698461</v>
       </c>
       <c r="R10" t="n">
-        <v>6646709</v>
+        <v>6646553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124457352</v>
+        <v>124474156</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,41 +1633,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698343</v>
+        <v>698340</v>
       </c>
       <c r="R11" t="n">
-        <v>6646433</v>
+        <v>6646487</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,22 +1715,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124474161</v>
+        <v>124474165</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,42 +1739,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698368</v>
+        <v>698508</v>
       </c>
       <c r="R12" t="n">
-        <v>6646487</v>
+        <v>6646430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1811,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1824,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124459239</v>
+        <v>124462750</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,47 +1841,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698474</v>
+        <v>698509</v>
       </c>
       <c r="R13" t="n">
-        <v>6646510</v>
+        <v>6646485</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1935,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124457671</v>
+        <v>124459075</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>30115</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,38 +1943,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>200985</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698365</v>
+        <v>698467</v>
       </c>
       <c r="R14" t="n">
-        <v>6646448</v>
+        <v>6646525</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,6 +2020,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2037,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462497</v>
+        <v>124474161</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,38 +2051,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698461</v>
+        <v>698368</v>
       </c>
       <c r="R15" t="n">
-        <v>6646553</v>
+        <v>6646487</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,25 +2127,26 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124474162</v>
+        <v>124459239</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2174,22 +2181,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698476</v>
+        <v>698474</v>
       </c>
       <c r="R16" t="n">
-        <v>6646591</v>
+        <v>6646510</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2227,29 +2239,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124457802</v>
+        <v>124457542</v>
       </c>
       <c r="B17" t="n">
-        <v>5196</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,21 +2273,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2286,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698365</v>
+        <v>698344</v>
       </c>
       <c r="R17" t="n">
-        <v>6646448</v>
+        <v>6646454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2348,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124474163</v>
+        <v>124461033</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>103528</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2360,42 +2371,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698473</v>
+        <v>698451</v>
       </c>
       <c r="R18" t="n">
-        <v>6646591</v>
+        <v>6646709</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,19 +2443,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2659,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462736</v>
+        <v>124474168</v>
       </c>
       <c r="B21" t="n">
-        <v>110163</v>
+        <v>100279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,37 +2681,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698509</v>
+        <v>698409</v>
       </c>
       <c r="R21" t="n">
-        <v>6646485</v>
+        <v>6646641</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2749,22 +2755,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124459075</v>
+        <v>124457802</v>
       </c>
       <c r="B22" t="n">
-        <v>30115</v>
+        <v>5196</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,39 +2783,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>200985</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698467</v>
+        <v>698365</v>
       </c>
       <c r="R22" t="n">
-        <v>6646525</v>
+        <v>6646448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2851,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124474164</v>
+        <v>124462736</v>
       </c>
       <c r="B23" t="n">
-        <v>105117</v>
+        <v>110163</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,37 +2885,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698354</v>
+        <v>698509</v>
       </c>
       <c r="R23" t="n">
-        <v>6646460</v>
+        <v>6646485</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,22 +2959,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124457542</v>
+        <v>124457671</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2983,25 +2983,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698344</v>
+        <v>698365</v>
       </c>
       <c r="R24" t="n">
-        <v>6646454</v>
+        <v>6646448</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124462497</v>
+        <v>124462750</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698461</v>
+        <v>698509</v>
       </c>
       <c r="R2" t="n">
-        <v>6646553</v>
+        <v>6646485</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124457678</v>
+        <v>124458289</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698365</v>
+        <v>698368</v>
       </c>
       <c r="R3" t="n">
-        <v>6646448</v>
+        <v>6646466</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124474163</v>
+        <v>124457484</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698473</v>
+        <v>698344</v>
       </c>
       <c r="R4" t="n">
-        <v>6646591</v>
+        <v>6646454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,29 +976,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474162</v>
+        <v>124474164</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,42 +1006,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698476</v>
+        <v>698354</v>
       </c>
       <c r="R5" t="n">
-        <v>6646591</v>
+        <v>6646460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124458289</v>
+        <v>124462473</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,53 +1108,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698368</v>
+        <v>698461</v>
       </c>
       <c r="R6" t="n">
-        <v>6646466</v>
+        <v>6646553</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1185,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124457969</v>
+        <v>124474162</v>
       </c>
       <c r="B7" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,41 +1215,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698343</v>
+        <v>698476</v>
       </c>
       <c r="R7" t="n">
-        <v>6646433</v>
+        <v>6646591</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,28 +1291,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124457352</v>
+        <v>124459239</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,38 +1322,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698343</v>
+        <v>698474</v>
       </c>
       <c r="R8" t="n">
-        <v>6646433</v>
+        <v>6646510</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1412,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124474164</v>
+        <v>124457969</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>98124</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,37 +1437,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698354</v>
+        <v>698343</v>
       </c>
       <c r="R9" t="n">
-        <v>6646460</v>
+        <v>6646433</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,22 +1511,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462473</v>
+        <v>124461033</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>103528</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,39 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698461</v>
+        <v>698451</v>
       </c>
       <c r="R10" t="n">
-        <v>6646553</v>
+        <v>6646709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474156</v>
+        <v>124474168</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,42 +1637,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698340</v>
+        <v>698409</v>
       </c>
       <c r="R11" t="n">
-        <v>6646487</v>
+        <v>6646641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124474165</v>
+        <v>124474156</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,38 +1739,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698508</v>
+        <v>698340</v>
       </c>
       <c r="R12" t="n">
-        <v>6646430</v>
+        <v>6646487</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124462750</v>
+        <v>124459075</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>30115</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,37 +1849,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698509</v>
+        <v>698467</v>
       </c>
       <c r="R13" t="n">
-        <v>6646485</v>
+        <v>6646525</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,6 +1922,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1931,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124459075</v>
+        <v>124474161</v>
       </c>
       <c r="B14" t="n">
-        <v>30115</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,43 +1953,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>200985</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698467</v>
+        <v>698368</v>
       </c>
       <c r="R14" t="n">
-        <v>6646525</v>
+        <v>6646487</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,22 +2036,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124474161</v>
+        <v>124457802</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>5196</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,42 +2060,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698368</v>
+        <v>698365</v>
       </c>
       <c r="R15" t="n">
-        <v>6646487</v>
+        <v>6646448</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,29 +2132,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124459239</v>
+        <v>124457678</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,50 +2162,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698474</v>
+        <v>698365</v>
       </c>
       <c r="R16" t="n">
-        <v>6646510</v>
+        <v>6646448</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2257,7 +2252,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124457542</v>
+        <v>124474165</v>
       </c>
       <c r="B17" t="n">
         <v>100279</v>
@@ -2293,14 +2288,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698344</v>
+        <v>698508</v>
       </c>
       <c r="R17" t="n">
-        <v>6646454</v>
+        <v>6646430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2347,22 +2342,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124461033</v>
+        <v>124474163</v>
       </c>
       <c r="B18" t="n">
-        <v>103528</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2371,38 +2366,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698451</v>
+        <v>698473</v>
       </c>
       <c r="R18" t="n">
-        <v>6646709</v>
+        <v>6646591</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,28 +2442,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124457484</v>
+        <v>124457671</v>
       </c>
       <c r="B19" t="n">
-        <v>105117</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2473,25 +2473,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698344</v>
+        <v>698365</v>
       </c>
       <c r="R19" t="n">
-        <v>6646454</v>
+        <v>6646448</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124474166</v>
+        <v>124457542</v>
       </c>
       <c r="B20" t="n">
         <v>100279</v>
@@ -2599,14 +2599,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698449</v>
+        <v>698344</v>
       </c>
       <c r="R20" t="n">
-        <v>6646765</v>
+        <v>6646454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,22 +2653,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124474168</v>
+        <v>124462736</v>
       </c>
       <c r="B21" t="n">
-        <v>100279</v>
+        <v>110163</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2681,37 +2681,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698409</v>
+        <v>698509</v>
       </c>
       <c r="R21" t="n">
-        <v>6646641</v>
+        <v>6646485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2755,22 +2755,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124457802</v>
+        <v>124474166</v>
       </c>
       <c r="B22" t="n">
-        <v>5196</v>
+        <v>100279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,34 +2783,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698365</v>
+        <v>698449</v>
       </c>
       <c r="R22" t="n">
-        <v>6646448</v>
+        <v>6646765</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,22 +2857,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462736</v>
+        <v>124462497</v>
       </c>
       <c r="B23" t="n">
-        <v>110163</v>
+        <v>100279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698509</v>
+        <v>698461</v>
       </c>
       <c r="R23" t="n">
-        <v>6646485</v>
+        <v>6646553</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124457671</v>
+        <v>124457352</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2983,25 +2983,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698365</v>
+        <v>698343</v>
       </c>
       <c r="R24" t="n">
-        <v>6646448</v>
+        <v>6646433</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124462750</v>
+        <v>124457484</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698509</v>
+        <v>698344</v>
       </c>
       <c r="R2" t="n">
-        <v>6646485</v>
+        <v>6646454</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124458289</v>
+        <v>124461033</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>103528</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,53 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698368</v>
+        <v>698451</v>
       </c>
       <c r="R3" t="n">
-        <v>6646466</v>
+        <v>6646709</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124457484</v>
+        <v>124457802</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>5196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698344</v>
+        <v>698365</v>
       </c>
       <c r="R4" t="n">
-        <v>6646454</v>
+        <v>6646448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474164</v>
+        <v>124474163</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,38 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698354</v>
+        <v>698473</v>
       </c>
       <c r="R5" t="n">
-        <v>6646460</v>
+        <v>6646591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1069,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1096,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124462473</v>
+        <v>124462736</v>
       </c>
       <c r="B6" t="n">
-        <v>5176</v>
+        <v>110163</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,42 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698461</v>
+        <v>698509</v>
       </c>
       <c r="R6" t="n">
-        <v>6646553</v>
+        <v>6646485</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124474162</v>
+        <v>124474156</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,42 +1202,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698476</v>
+        <v>698340</v>
       </c>
       <c r="R7" t="n">
-        <v>6646591</v>
+        <v>6646487</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1278,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1310,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124459239</v>
+        <v>124462473</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,50 +1308,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698474</v>
+        <v>698461</v>
       </c>
       <c r="R8" t="n">
-        <v>6646510</v>
+        <v>6646553</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124457969</v>
+        <v>124474166</v>
       </c>
       <c r="B9" t="n">
-        <v>98124</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,37 +1419,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698343</v>
+        <v>698449</v>
       </c>
       <c r="R9" t="n">
-        <v>6646433</v>
+        <v>6646765</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,22 +1493,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124461033</v>
+        <v>124457352</v>
       </c>
       <c r="B10" t="n">
-        <v>103528</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,16 +1521,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1559,17 +1541,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698451</v>
+        <v>698343</v>
       </c>
       <c r="R10" t="n">
-        <v>6646709</v>
+        <v>6646433</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1625,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474168</v>
+        <v>124459239</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,41 +1619,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698409</v>
+        <v>698474</v>
       </c>
       <c r="R11" t="n">
-        <v>6646641</v>
+        <v>6646510</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1715,22 +1706,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124474156</v>
+        <v>124458289</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,45 +1730,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698340</v>
+        <v>698368</v>
       </c>
       <c r="R12" t="n">
-        <v>6646487</v>
+        <v>6646466</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,28 +1814,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124459075</v>
+        <v>124457542</v>
       </c>
       <c r="B13" t="n">
-        <v>30115</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,39 +1849,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>200985</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698467</v>
+        <v>698344</v>
       </c>
       <c r="R13" t="n">
-        <v>6646525</v>
+        <v>6646454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1917,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1941,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474161</v>
+        <v>124474165</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1953,42 +1947,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698368</v>
+        <v>698508</v>
       </c>
       <c r="R14" t="n">
-        <v>6646487</v>
+        <v>6646430</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2019,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2048,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124457802</v>
+        <v>124474161</v>
       </c>
       <c r="B15" t="n">
-        <v>5196</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2060,38 +2049,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698365</v>
+        <v>698368</v>
       </c>
       <c r="R15" t="n">
-        <v>6646448</v>
+        <v>6646487</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,28 +2125,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124457678</v>
+        <v>124462750</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,37 +2160,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698365</v>
+        <v>698509</v>
       </c>
       <c r="R16" t="n">
-        <v>6646448</v>
+        <v>6646485</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2252,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124474165</v>
+        <v>124457969</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>98124</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,37 +2262,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698508</v>
+        <v>698343</v>
       </c>
       <c r="R17" t="n">
-        <v>6646430</v>
+        <v>6646433</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2342,22 +2336,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124474163</v>
+        <v>124462497</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,42 +2360,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698473</v>
+        <v>698461</v>
       </c>
       <c r="R18" t="n">
-        <v>6646591</v>
+        <v>6646553</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,29 +2432,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124457671</v>
+        <v>124457678</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2473,25 +2462,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2563,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124457542</v>
+        <v>124457671</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2575,25 +2564,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2603,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698344</v>
+        <v>698365</v>
       </c>
       <c r="R20" t="n">
-        <v>6646454</v>
+        <v>6646448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,10 +2654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462736</v>
+        <v>124474162</v>
       </c>
       <c r="B21" t="n">
-        <v>110163</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,41 +2666,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698509</v>
+        <v>698476</v>
       </c>
       <c r="R21" t="n">
-        <v>6646485</v>
+        <v>6646591</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2749,28 +2742,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124474166</v>
+        <v>124474164</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,21 +2777,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2807,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698449</v>
+        <v>698354</v>
       </c>
       <c r="R22" t="n">
-        <v>6646765</v>
+        <v>6646460</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462497</v>
+        <v>124459075</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>30115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,34 +2879,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698461</v>
+        <v>698467</v>
       </c>
       <c r="R23" t="n">
-        <v>6646553</v>
+        <v>6646525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,6 +2952,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124457352</v>
+        <v>124474168</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,37 +2987,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698343</v>
+        <v>698409</v>
       </c>
       <c r="R24" t="n">
-        <v>6646433</v>
+        <v>6646641</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457484</v>
+        <v>124457969</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>98124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698344</v>
+        <v>698343</v>
       </c>
       <c r="R2" t="n">
-        <v>6646454</v>
+        <v>6646433</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124461033</v>
+        <v>124474168</v>
       </c>
       <c r="B3" t="n">
-        <v>103528</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698451</v>
+        <v>698409</v>
       </c>
       <c r="R3" t="n">
-        <v>6646709</v>
+        <v>6646641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124457802</v>
+        <v>124461033</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>103528</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698365</v>
+        <v>698451</v>
       </c>
       <c r="R4" t="n">
-        <v>6646448</v>
+        <v>6646709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474163</v>
+        <v>124474161</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>158</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698473</v>
+        <v>698368</v>
       </c>
       <c r="R5" t="n">
-        <v>6646591</v>
+        <v>6646487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124462736</v>
+        <v>124474156</v>
       </c>
       <c r="B6" t="n">
-        <v>110163</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1100,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698509</v>
+        <v>698340</v>
       </c>
       <c r="R6" t="n">
-        <v>6646485</v>
+        <v>6646487</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124474156</v>
+        <v>124459239</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,45 +1206,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698340</v>
+        <v>698474</v>
       </c>
       <c r="R7" t="n">
-        <v>6646487</v>
+        <v>6646510</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,22 +1293,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124462473</v>
+        <v>124462736</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>110163</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,42 +1321,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698461</v>
+        <v>698509</v>
       </c>
       <c r="R8" t="n">
-        <v>6646553</v>
+        <v>6646485</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124474166</v>
+        <v>124474165</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1443,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698449</v>
+        <v>698508</v>
       </c>
       <c r="R9" t="n">
-        <v>6646765</v>
+        <v>6646430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124457352</v>
+        <v>124462473</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,37 +1525,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698343</v>
+        <v>698461</v>
       </c>
       <c r="R10" t="n">
-        <v>6646433</v>
+        <v>6646553</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124459239</v>
+        <v>124457802</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>5196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,50 +1628,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698474</v>
+        <v>698365</v>
       </c>
       <c r="R11" t="n">
-        <v>6646510</v>
+        <v>6646448</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124458289</v>
+        <v>124474166</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,53 +1730,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698368</v>
+        <v>698449</v>
       </c>
       <c r="R12" t="n">
-        <v>6646466</v>
+        <v>6646765</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,29 +1802,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124457542</v>
+        <v>124457671</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,25 +1832,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698344</v>
+        <v>698365</v>
       </c>
       <c r="R13" t="n">
-        <v>6646454</v>
+        <v>6646448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474165</v>
+        <v>124458289</v>
       </c>
       <c r="B14" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,41 +1934,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698508</v>
+        <v>698368</v>
       </c>
       <c r="R14" t="n">
-        <v>6646430</v>
+        <v>6646466</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,25 +2018,26 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124474161</v>
+        <v>124474163</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698368</v>
+        <v>698473</v>
       </c>
       <c r="R15" t="n">
-        <v>6646487</v>
+        <v>6646591</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462750</v>
+        <v>124459075</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>30115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,37 +2160,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698509</v>
+        <v>698467</v>
       </c>
       <c r="R16" t="n">
-        <v>6646485</v>
+        <v>6646525</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2228,6 +2233,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2246,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124457969</v>
+        <v>124462750</v>
       </c>
       <c r="B17" t="n">
-        <v>98124</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,34 +2268,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698343</v>
+        <v>698509</v>
       </c>
       <c r="R17" t="n">
-        <v>6646433</v>
+        <v>6646485</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2348,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124462497</v>
+        <v>124457678</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,34 +2370,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698461</v>
+        <v>698365</v>
       </c>
       <c r="R18" t="n">
-        <v>6646553</v>
+        <v>6646448</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124457678</v>
+        <v>124474164</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>105117</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,34 +2472,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698365</v>
+        <v>698354</v>
       </c>
       <c r="R19" t="n">
-        <v>6646448</v>
+        <v>6646460</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,22 +2546,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124457671</v>
+        <v>124462497</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2564,38 +2570,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698365</v>
+        <v>698461</v>
       </c>
       <c r="R20" t="n">
-        <v>6646448</v>
+        <v>6646553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124474162</v>
+        <v>124457484</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2666,42 +2672,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698476</v>
+        <v>698344</v>
       </c>
       <c r="R21" t="n">
-        <v>6646591</v>
+        <v>6646454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,29 +2744,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124474164</v>
+        <v>124474162</v>
       </c>
       <c r="B22" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,38 +2774,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698354</v>
+        <v>698476</v>
       </c>
       <c r="R22" t="n">
-        <v>6646460</v>
+        <v>6646591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2845,6 +2850,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2863,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124459075</v>
+        <v>124457542</v>
       </c>
       <c r="B23" t="n">
-        <v>30115</v>
+        <v>100279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,39 +2885,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>200985</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698467</v>
+        <v>698344</v>
       </c>
       <c r="R23" t="n">
-        <v>6646525</v>
+        <v>6646454</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2952,7 +2953,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124474168</v>
+        <v>124457352</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,37 +2987,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698409</v>
+        <v>698343</v>
       </c>
       <c r="R24" t="n">
-        <v>6646641</v>
+        <v>6646433</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457969</v>
+        <v>124457802</v>
       </c>
       <c r="B2" t="n">
-        <v>98124</v>
+        <v>5196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698343</v>
+        <v>698365</v>
       </c>
       <c r="R2" t="n">
-        <v>6646433</v>
+        <v>6646448</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124474168</v>
+        <v>124459075</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>30115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698409</v>
+        <v>698467</v>
       </c>
       <c r="R3" t="n">
-        <v>6646641</v>
+        <v>6646525</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,28 +866,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124461033</v>
+        <v>124457352</v>
       </c>
       <c r="B4" t="n">
-        <v>103528</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +901,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -915,17 +921,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698451</v>
+        <v>698343</v>
       </c>
       <c r="R4" t="n">
-        <v>6646709</v>
+        <v>6646433</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474161</v>
+        <v>124462473</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +999,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>158</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698368</v>
+        <v>698461</v>
       </c>
       <c r="R5" t="n">
-        <v>6646487</v>
+        <v>6646553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,29 +1076,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124474156</v>
+        <v>124474161</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,39 +1106,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698340</v>
+        <v>698368</v>
       </c>
       <c r="R6" t="n">
         <v>6646487</v>
@@ -1176,6 +1182,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,7 +1201,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124459239</v>
+        <v>124474162</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1229,27 +1236,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698474</v>
+        <v>698476</v>
       </c>
       <c r="R7" t="n">
-        <v>6646510</v>
+        <v>6646591</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,28 +1289,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124462736</v>
+        <v>124474166</v>
       </c>
       <c r="B8" t="n">
-        <v>110163</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,37 +1324,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698509</v>
+        <v>698449</v>
       </c>
       <c r="R8" t="n">
-        <v>6646485</v>
+        <v>6646765</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,22 +1398,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124474165</v>
+        <v>124459239</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,41 +1422,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698508</v>
+        <v>698474</v>
       </c>
       <c r="R9" t="n">
-        <v>6646430</v>
+        <v>6646510</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,22 +1509,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462473</v>
+        <v>124457969</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,42 +1537,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698461</v>
+        <v>698343</v>
       </c>
       <c r="R10" t="n">
-        <v>6646553</v>
+        <v>6646433</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124457802</v>
+        <v>124474163</v>
       </c>
       <c r="B11" t="n">
-        <v>5196</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,38 +1635,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698365</v>
+        <v>698473</v>
       </c>
       <c r="R11" t="n">
-        <v>6646448</v>
+        <v>6646591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,25 +1711,26 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124474166</v>
+        <v>124462750</v>
       </c>
       <c r="B12" t="n">
         <v>100279</v>
@@ -1754,17 +1766,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698449</v>
+        <v>698509</v>
       </c>
       <c r="R12" t="n">
-        <v>6646765</v>
+        <v>6646485</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,22 +1820,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124457671</v>
+        <v>124457484</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>105117</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698365</v>
+        <v>698344</v>
       </c>
       <c r="R13" t="n">
-        <v>6646448</v>
+        <v>6646454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124458289</v>
+        <v>124457542</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,53 +1946,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698368</v>
+        <v>698344</v>
       </c>
       <c r="R14" t="n">
-        <v>6646466</v>
+        <v>6646454</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2018,7 +2018,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2037,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124474163</v>
+        <v>124457671</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,42 +2048,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698473</v>
+        <v>698365</v>
       </c>
       <c r="R15" t="n">
-        <v>6646591</v>
+        <v>6646448</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,29 +2120,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124459075</v>
+        <v>124458289</v>
       </c>
       <c r="B16" t="n">
-        <v>30115</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2156,32 +2150,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>200985</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2189,13 +2190,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698467</v>
+        <v>698368</v>
       </c>
       <c r="R16" t="n">
-        <v>6646525</v>
+        <v>6646466</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462750</v>
+        <v>124474164</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,37 +2269,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698509</v>
+        <v>698354</v>
       </c>
       <c r="R17" t="n">
-        <v>6646485</v>
+        <v>6646460</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2342,22 +2343,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124457678</v>
+        <v>124462497</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,34 +2371,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698365</v>
+        <v>698461</v>
       </c>
       <c r="R18" t="n">
-        <v>6646448</v>
+        <v>6646553</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,10 +2457,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124474164</v>
+        <v>124474156</v>
       </c>
       <c r="B19" t="n">
-        <v>105117</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2468,38 +2469,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698354</v>
+        <v>698340</v>
       </c>
       <c r="R19" t="n">
-        <v>6646460</v>
+        <v>6646487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,7 +2563,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462497</v>
+        <v>124474168</v>
       </c>
       <c r="B20" t="n">
         <v>100279</v>
@@ -2594,14 +2599,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698461</v>
+        <v>698409</v>
       </c>
       <c r="R20" t="n">
-        <v>6646553</v>
+        <v>6646641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,22 +2653,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124457484</v>
+        <v>124461033</v>
       </c>
       <c r="B21" t="n">
-        <v>105117</v>
+        <v>103528</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,34 +2681,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698344</v>
+        <v>698451</v>
       </c>
       <c r="R21" t="n">
-        <v>6646454</v>
+        <v>6646709</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124474162</v>
+        <v>124457678</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,42 +2779,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698476</v>
+        <v>698365</v>
       </c>
       <c r="R22" t="n">
-        <v>6646591</v>
+        <v>6646448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,29 +2851,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124457542</v>
+        <v>124462736</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>110163</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,37 +2885,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698344</v>
+        <v>698509</v>
       </c>
       <c r="R23" t="n">
-        <v>6646454</v>
+        <v>6646485</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124457352</v>
+        <v>124474165</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,37 +2987,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698343</v>
+        <v>698508</v>
       </c>
       <c r="R24" t="n">
-        <v>6646433</v>
+        <v>6646430</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457802</v>
+        <v>124457969</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>98124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698365</v>
+        <v>698343</v>
       </c>
       <c r="R2" t="n">
-        <v>6646448</v>
+        <v>6646433</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124459075</v>
+        <v>124457352</v>
       </c>
       <c r="B3" t="n">
-        <v>30115</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>200985</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698467</v>
+        <v>698343</v>
       </c>
       <c r="R3" t="n">
-        <v>6646525</v>
+        <v>6646433</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124457352</v>
+        <v>124474156</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,41 +891,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698343</v>
+        <v>698340</v>
       </c>
       <c r="R4" t="n">
-        <v>6646433</v>
+        <v>6646487</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124462473</v>
+        <v>124474161</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,43 +997,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698461</v>
+        <v>698368</v>
       </c>
       <c r="R5" t="n">
-        <v>6646553</v>
+        <v>6646487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,25 +1073,26 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124474161</v>
+        <v>124474163</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1129,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1138,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698368</v>
+        <v>698473</v>
       </c>
       <c r="R6" t="n">
-        <v>6646487</v>
+        <v>6646591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124474166</v>
+        <v>124457678</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,34 +1322,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698449</v>
+        <v>698365</v>
       </c>
       <c r="R8" t="n">
-        <v>6646765</v>
+        <v>6646448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,22 +1396,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124459239</v>
+        <v>124459075</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>30115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,50 +1420,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>200985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698474</v>
+        <v>698467</v>
       </c>
       <c r="R9" t="n">
-        <v>6646510</v>
+        <v>6646525</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1503,6 +1497,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124457969</v>
+        <v>124461033</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>103528</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,37 +1532,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698343</v>
+        <v>698451</v>
       </c>
       <c r="R10" t="n">
-        <v>6646433</v>
+        <v>6646709</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474163</v>
+        <v>124457671</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,42 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698473</v>
+        <v>698365</v>
       </c>
       <c r="R11" t="n">
-        <v>6646591</v>
+        <v>6646448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,29 +1702,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462750</v>
+        <v>124462473</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,37 +1736,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698509</v>
+        <v>698461</v>
       </c>
       <c r="R12" t="n">
-        <v>6646485</v>
+        <v>6646553</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1832,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124457484</v>
+        <v>124457802</v>
       </c>
       <c r="B13" t="n">
-        <v>105117</v>
+        <v>5196</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698344</v>
+        <v>698365</v>
       </c>
       <c r="R13" t="n">
-        <v>6646454</v>
+        <v>6646448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124457542</v>
+        <v>124474165</v>
       </c>
       <c r="B14" t="n">
         <v>100279</v>
@@ -1970,14 +1965,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698344</v>
+        <v>698508</v>
       </c>
       <c r="R14" t="n">
-        <v>6646454</v>
+        <v>6646430</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124457671</v>
+        <v>124474164</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>105117</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,38 +2043,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698365</v>
+        <v>698354</v>
       </c>
       <c r="R15" t="n">
-        <v>6646448</v>
+        <v>6646460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,22 +2121,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124458289</v>
+        <v>124462497</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,53 +2145,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698368</v>
+        <v>698461</v>
       </c>
       <c r="R16" t="n">
-        <v>6646466</v>
+        <v>6646553</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2234,7 +2217,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2253,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124474164</v>
+        <v>124459239</v>
       </c>
       <c r="B17" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,41 +2247,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698354</v>
+        <v>698474</v>
       </c>
       <c r="R17" t="n">
-        <v>6646460</v>
+        <v>6646510</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2343,19 +2334,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124462497</v>
+        <v>124474168</v>
       </c>
       <c r="B18" t="n">
         <v>100279</v>
@@ -2391,14 +2382,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698461</v>
+        <v>698409</v>
       </c>
       <c r="R18" t="n">
-        <v>6646553</v>
+        <v>6646641</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,22 +2436,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124474156</v>
+        <v>124462736</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>110163</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,45 +2460,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698340</v>
+        <v>698509</v>
       </c>
       <c r="R19" t="n">
-        <v>6646487</v>
+        <v>6646485</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2551,19 +2538,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124474168</v>
+        <v>124457542</v>
       </c>
       <c r="B20" t="n">
         <v>100279</v>
@@ -2599,14 +2586,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698409</v>
+        <v>698344</v>
       </c>
       <c r="R20" t="n">
-        <v>6646641</v>
+        <v>6646454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,22 +2640,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124461033</v>
+        <v>124474166</v>
       </c>
       <c r="B21" t="n">
-        <v>103528</v>
+        <v>100279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2681,34 +2668,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698451</v>
+        <v>698449</v>
       </c>
       <c r="R21" t="n">
-        <v>6646709</v>
+        <v>6646765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,22 +2742,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124457678</v>
+        <v>124458289</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,41 +2766,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698365</v>
+        <v>698368</v>
       </c>
       <c r="R22" t="n">
-        <v>6646448</v>
+        <v>6646466</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2851,6 +2850,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462736</v>
+        <v>124457484</v>
       </c>
       <c r="B23" t="n">
-        <v>110163</v>
+        <v>105117</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,37 +2885,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698509</v>
+        <v>698344</v>
       </c>
       <c r="R23" t="n">
-        <v>6646485</v>
+        <v>6646454</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124474165</v>
+        <v>124462750</v>
       </c>
       <c r="B24" t="n">
         <v>100279</v>
@@ -3007,17 +3007,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698508</v>
+        <v>698509</v>
       </c>
       <c r="R24" t="n">
-        <v>6646430</v>
+        <v>6646485</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -985,7 +985,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474161</v>
+        <v>124474162</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698368</v>
+        <v>698476</v>
       </c>
       <c r="R5" t="n">
-        <v>6646487</v>
+        <v>6646591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124474163</v>
+        <v>124474161</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>158</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698473</v>
+        <v>698368</v>
       </c>
       <c r="R6" t="n">
-        <v>6646591</v>
+        <v>6646487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124474162</v>
+        <v>124474163</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698476</v>
+        <v>698473</v>
       </c>
       <c r="R7" t="n">
         <v>6646591</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124461033</v>
+        <v>124457671</v>
       </c>
       <c r="B10" t="n">
-        <v>103528</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,38 +1528,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698451</v>
+        <v>698365</v>
       </c>
       <c r="R10" t="n">
-        <v>6646709</v>
+        <v>6646448</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124457671</v>
+        <v>124461033</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>103528</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,38 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698365</v>
+        <v>698451</v>
       </c>
       <c r="R11" t="n">
-        <v>6646448</v>
+        <v>6646709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462473</v>
+        <v>124457802</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,39 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698461</v>
+        <v>698365</v>
       </c>
       <c r="R12" t="n">
-        <v>6646553</v>
+        <v>6646448</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124457802</v>
+        <v>124462473</v>
       </c>
       <c r="B13" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,34 +1838,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698365</v>
+        <v>698461</v>
       </c>
       <c r="R13" t="n">
-        <v>6646448</v>
+        <v>6646553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124458289</v>
+        <v>124457484</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,53 +2766,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698368</v>
+        <v>698344</v>
       </c>
       <c r="R22" t="n">
-        <v>6646466</v>
+        <v>6646454</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2850,7 +2838,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2869,10 +2856,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124457484</v>
+        <v>124458289</v>
       </c>
       <c r="B23" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2881,41 +2868,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698344</v>
+        <v>698368</v>
       </c>
       <c r="R23" t="n">
-        <v>6646454</v>
+        <v>6646466</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2953,6 +2952,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457969</v>
+        <v>124462750</v>
       </c>
       <c r="B2" t="n">
-        <v>98124</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698343</v>
+        <v>698509</v>
       </c>
       <c r="R2" t="n">
-        <v>6646433</v>
+        <v>6646485</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124457352</v>
+        <v>124462736</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>110163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698343</v>
+        <v>698509</v>
       </c>
       <c r="R3" t="n">
-        <v>6646433</v>
+        <v>6646485</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124474156</v>
+        <v>124457802</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>5196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,20 +891,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,20 +913,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698340</v>
+        <v>698365</v>
       </c>
       <c r="R4" t="n">
-        <v>6646487</v>
+        <v>6646448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474162</v>
+        <v>124474156</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698476</v>
+        <v>698340</v>
       </c>
       <c r="R5" t="n">
-        <v>6646591</v>
+        <v>6646487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1069,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124474161</v>
+        <v>124474166</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,42 +1099,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698368</v>
+        <v>698449</v>
       </c>
       <c r="R6" t="n">
-        <v>6646487</v>
+        <v>6646765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1171,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1199,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124474163</v>
+        <v>124462473</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,42 +1201,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698473</v>
+        <v>698461</v>
       </c>
       <c r="R7" t="n">
-        <v>6646591</v>
+        <v>6646553</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,29 +1278,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124457678</v>
+        <v>124457352</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698365</v>
+        <v>698343</v>
       </c>
       <c r="R8" t="n">
-        <v>6646448</v>
+        <v>6646433</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124459075</v>
+        <v>124457969</v>
       </c>
       <c r="B9" t="n">
-        <v>30115</v>
+        <v>98124</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,42 +1414,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>200985</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698467</v>
+        <v>698343</v>
       </c>
       <c r="R9" t="n">
-        <v>6646525</v>
+        <v>6646433</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,7 +1482,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1516,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124457671</v>
+        <v>124474161</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,38 +1512,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698365</v>
+        <v>698368</v>
       </c>
       <c r="R10" t="n">
-        <v>6646448</v>
+        <v>6646487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,28 +1588,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124461033</v>
+        <v>124457678</v>
       </c>
       <c r="B11" t="n">
-        <v>103528</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,34 +1623,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698451</v>
+        <v>698365</v>
       </c>
       <c r="R11" t="n">
-        <v>6646709</v>
+        <v>6646448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124457802</v>
+        <v>124457671</v>
       </c>
       <c r="B12" t="n">
-        <v>5196</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1721,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1822,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124462473</v>
+        <v>124457484</v>
       </c>
       <c r="B13" t="n">
-        <v>5176</v>
+        <v>105117</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,39 +1827,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698461</v>
+        <v>698344</v>
       </c>
       <c r="R13" t="n">
-        <v>6646553</v>
+        <v>6646454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474165</v>
+        <v>124474164</v>
       </c>
       <c r="B14" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698508</v>
+        <v>698354</v>
       </c>
       <c r="R14" t="n">
-        <v>6646430</v>
+        <v>6646460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124474164</v>
+        <v>124458289</v>
       </c>
       <c r="B15" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,41 +2027,53 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698354</v>
+        <v>698368</v>
       </c>
       <c r="R15" t="n">
-        <v>6646460</v>
+        <v>6646466</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2115,28 +2111,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462497</v>
+        <v>124459075</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>30115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,34 +2146,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698461</v>
+        <v>698467</v>
       </c>
       <c r="R16" t="n">
-        <v>6646553</v>
+        <v>6646525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2217,6 +2219,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2346,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124474168</v>
+        <v>124474163</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,38 +2361,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698409</v>
+        <v>698473</v>
       </c>
       <c r="R18" t="n">
-        <v>6646641</v>
+        <v>6646591</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2430,6 +2437,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2448,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462736</v>
+        <v>124462497</v>
       </c>
       <c r="B19" t="n">
-        <v>110163</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,21 +2472,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2488,13 +2496,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698509</v>
+        <v>698461</v>
       </c>
       <c r="R19" t="n">
-        <v>6646485</v>
+        <v>6646553</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,7 +2558,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124457542</v>
+        <v>124474168</v>
       </c>
       <c r="B20" t="n">
         <v>100279</v>
@@ -2586,14 +2594,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698344</v>
+        <v>698409</v>
       </c>
       <c r="R20" t="n">
-        <v>6646454</v>
+        <v>6646641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,22 +2648,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124474166</v>
+        <v>124461033</v>
       </c>
       <c r="B21" t="n">
-        <v>100279</v>
+        <v>103528</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2668,34 +2676,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698449</v>
+        <v>698451</v>
       </c>
       <c r="R21" t="n">
-        <v>6646765</v>
+        <v>6646709</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,22 +2750,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124457484</v>
+        <v>124474165</v>
       </c>
       <c r="B22" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2770,34 +2778,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698344</v>
+        <v>698508</v>
       </c>
       <c r="R22" t="n">
-        <v>6646454</v>
+        <v>6646430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2844,19 +2852,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124458289</v>
+        <v>124474162</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2891,30 +2899,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698368</v>
+        <v>698476</v>
       </c>
       <c r="R23" t="n">
-        <v>6646466</v>
+        <v>6646591</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,19 +2959,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124462750</v>
+        <v>124457542</v>
       </c>
       <c r="B24" t="n">
         <v>100279</v>
@@ -3007,17 +3007,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698509</v>
+        <v>698344</v>
       </c>
       <c r="R24" t="n">
-        <v>6646485</v>
+        <v>6646454</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124462473</v>
+        <v>124457969</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>98124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,42 +1205,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698461</v>
+        <v>698343</v>
       </c>
       <c r="R7" t="n">
-        <v>6646553</v>
+        <v>6646433</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124457352</v>
+        <v>124462473</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,37 +1307,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698343</v>
+        <v>698461</v>
       </c>
       <c r="R8" t="n">
-        <v>6646433</v>
+        <v>6646553</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124457969</v>
+        <v>124457352</v>
       </c>
       <c r="B9" t="n">
-        <v>98124</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124474165</v>
+        <v>124474162</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,38 +2774,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698508</v>
+        <v>698476</v>
       </c>
       <c r="R22" t="n">
-        <v>6646430</v>
+        <v>6646591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,6 +2850,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2864,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124474162</v>
+        <v>124474165</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2876,42 +2881,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698476</v>
+        <v>698508</v>
       </c>
       <c r="R23" t="n">
-        <v>6646591</v>
+        <v>6646430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2952,7 +2953,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124462750</v>
+        <v>124457352</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698509</v>
+        <v>698343</v>
       </c>
       <c r="R2" t="n">
-        <v>6646485</v>
+        <v>6646433</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124462736</v>
+        <v>124474156</v>
       </c>
       <c r="B3" t="n">
-        <v>110163</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698509</v>
+        <v>698340</v>
       </c>
       <c r="R3" t="n">
-        <v>6646485</v>
+        <v>6646487</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +871,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124457802</v>
+        <v>124474166</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698365</v>
+        <v>698449</v>
       </c>
       <c r="R4" t="n">
-        <v>6646448</v>
+        <v>6646765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474156</v>
+        <v>124474161</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,39 +997,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698340</v>
+        <v>698368</v>
       </c>
       <c r="R5" t="n">
         <v>6646487</v>
@@ -1069,6 +1073,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124474166</v>
+        <v>124474163</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1104,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698449</v>
+        <v>698473</v>
       </c>
       <c r="R6" t="n">
-        <v>6646765</v>
+        <v>6646591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,6 +1180,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124457969</v>
+        <v>124461033</v>
       </c>
       <c r="B7" t="n">
-        <v>98124</v>
+        <v>103528</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,37 +1215,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698343</v>
+        <v>698451</v>
       </c>
       <c r="R7" t="n">
-        <v>6646433</v>
+        <v>6646709</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124462473</v>
+        <v>124474164</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,39 +1317,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698461</v>
+        <v>698354</v>
       </c>
       <c r="R8" t="n">
-        <v>6646553</v>
+        <v>6646460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,22 +1391,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124457352</v>
+        <v>124459239</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,38 +1415,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698343</v>
+        <v>698474</v>
       </c>
       <c r="R9" t="n">
-        <v>6646433</v>
+        <v>6646510</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124474161</v>
+        <v>124462473</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,42 +1526,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>158</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698368</v>
+        <v>698461</v>
       </c>
       <c r="R10" t="n">
-        <v>6646487</v>
+        <v>6646553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,19 +1603,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1709,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124457671</v>
+        <v>124462497</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,38 +1735,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698365</v>
+        <v>698461</v>
       </c>
       <c r="R12" t="n">
-        <v>6646448</v>
+        <v>6646553</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124457484</v>
+        <v>124474168</v>
       </c>
       <c r="B13" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,34 +1841,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698344</v>
+        <v>698409</v>
       </c>
       <c r="R13" t="n">
-        <v>6646454</v>
+        <v>6646641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,19 +1915,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474164</v>
+        <v>124457484</v>
       </c>
       <c r="B14" t="n">
         <v>105117</v>
@@ -1949,14 +1963,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698354</v>
+        <v>698344</v>
       </c>
       <c r="R14" t="n">
-        <v>6646460</v>
+        <v>6646454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,22 +2017,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124458289</v>
+        <v>124457969</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,50 +2041,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698368</v>
+        <v>698343</v>
       </c>
       <c r="R15" t="n">
-        <v>6646466</v>
+        <v>6646433</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2111,7 +2113,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124459075</v>
+        <v>124457542</v>
       </c>
       <c r="B16" t="n">
-        <v>30115</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2146,39 +2147,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>200985</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698467</v>
+        <v>698344</v>
       </c>
       <c r="R16" t="n">
-        <v>6646525</v>
+        <v>6646454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,7 +2215,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2238,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124459239</v>
+        <v>124457671</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,50 +2245,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698474</v>
+        <v>698365</v>
       </c>
       <c r="R17" t="n">
-        <v>6646510</v>
+        <v>6646448</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124474163</v>
+        <v>124459075</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>30115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,42 +2347,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>200985</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698473</v>
+        <v>698467</v>
       </c>
       <c r="R18" t="n">
-        <v>6646591</v>
+        <v>6646525</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,22 +2431,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462497</v>
+        <v>124462736</v>
       </c>
       <c r="B19" t="n">
-        <v>100279</v>
+        <v>110163</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,21 +2459,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,13 +2483,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698461</v>
+        <v>698509</v>
       </c>
       <c r="R19" t="n">
-        <v>6646553</v>
+        <v>6646485</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2558,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124474168</v>
+        <v>124458289</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,41 +2557,53 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698409</v>
+        <v>698368</v>
       </c>
       <c r="R20" t="n">
-        <v>6646641</v>
+        <v>6646466</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2642,28 +2641,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124461033</v>
+        <v>124462750</v>
       </c>
       <c r="B21" t="n">
-        <v>103528</v>
+        <v>100279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698451</v>
+        <v>698509</v>
       </c>
       <c r="R21" t="n">
-        <v>6646709</v>
+        <v>6646485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124474165</v>
+        <v>124457802</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,34 +2885,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698508</v>
+        <v>698365</v>
       </c>
       <c r="R23" t="n">
-        <v>6646430</v>
+        <v>6646448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2959,19 +2959,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124457542</v>
+        <v>124474165</v>
       </c>
       <c r="B24" t="n">
         <v>100279</v>
@@ -3007,14 +3007,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698344</v>
+        <v>698508</v>
       </c>
       <c r="R24" t="n">
-        <v>6646454</v>
+        <v>6646430</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457352</v>
+        <v>124457678</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698343</v>
+        <v>698365</v>
       </c>
       <c r="R2" t="n">
-        <v>6646433</v>
+        <v>6646448</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124474156</v>
+        <v>124457671</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698340</v>
+        <v>698365</v>
       </c>
       <c r="R3" t="n">
-        <v>6646487</v>
+        <v>6646448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124474166</v>
+        <v>124474156</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698449</v>
+        <v>698340</v>
       </c>
       <c r="R4" t="n">
-        <v>6646765</v>
+        <v>6646487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474161</v>
+        <v>124462473</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +997,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>158</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698368</v>
+        <v>698461</v>
       </c>
       <c r="R5" t="n">
-        <v>6646487</v>
+        <v>6646553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,29 +1074,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124474163</v>
+        <v>124462750</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,45 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698473</v>
+        <v>698509</v>
       </c>
       <c r="R6" t="n">
-        <v>6646591</v>
+        <v>6646485</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,29 +1176,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124461033</v>
+        <v>124458289</v>
       </c>
       <c r="B7" t="n">
-        <v>103528</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,41 +1206,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698451</v>
+        <v>698368</v>
       </c>
       <c r="R7" t="n">
-        <v>6646709</v>
+        <v>6646466</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,6 +1290,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1403,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124459239</v>
+        <v>124459075</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>30115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,50 +1423,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>200985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698474</v>
+        <v>698467</v>
       </c>
       <c r="R9" t="n">
-        <v>6646510</v>
+        <v>6646525</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,6 +1500,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1514,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462473</v>
+        <v>124474163</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,43 +1531,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698461</v>
+        <v>698473</v>
       </c>
       <c r="R10" t="n">
-        <v>6646553</v>
+        <v>6646591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,28 +1607,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124457678</v>
+        <v>124474168</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,34 +1642,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698365</v>
+        <v>698409</v>
       </c>
       <c r="R11" t="n">
-        <v>6646448</v>
+        <v>6646641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,12 +1716,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1825,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124474168</v>
+        <v>124457484</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698409</v>
+        <v>698344</v>
       </c>
       <c r="R13" t="n">
-        <v>6646641</v>
+        <v>6646454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,22 +1920,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124457484</v>
+        <v>124474165</v>
       </c>
       <c r="B14" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,34 +1948,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698344</v>
+        <v>698508</v>
       </c>
       <c r="R14" t="n">
-        <v>6646454</v>
+        <v>6646430</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,22 +2022,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124457969</v>
+        <v>124474161</v>
       </c>
       <c r="B15" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,41 +2046,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698343</v>
+        <v>698368</v>
       </c>
       <c r="R15" t="n">
-        <v>6646433</v>
+        <v>6646487</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2113,28 +2122,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124457542</v>
+        <v>124457352</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2157,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,13 +2181,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698344</v>
+        <v>698343</v>
       </c>
       <c r="R16" t="n">
-        <v>6646454</v>
+        <v>6646433</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2233,10 +2243,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124457671</v>
+        <v>124457542</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,25 +2255,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2283,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698365</v>
+        <v>698344</v>
       </c>
       <c r="R17" t="n">
-        <v>6646448</v>
+        <v>6646454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124459075</v>
+        <v>124474162</v>
       </c>
       <c r="B18" t="n">
-        <v>30115</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,43 +2357,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>200985</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698467</v>
+        <v>698476</v>
       </c>
       <c r="R18" t="n">
-        <v>6646525</v>
+        <v>6646591</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2431,22 +2440,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462736</v>
+        <v>124474166</v>
       </c>
       <c r="B19" t="n">
-        <v>110163</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2459,37 +2468,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698509</v>
+        <v>698449</v>
       </c>
       <c r="R19" t="n">
-        <v>6646485</v>
+        <v>6646765</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2533,22 +2542,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124458289</v>
+        <v>124457802</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>5196</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,53 +2566,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698368</v>
+        <v>698365</v>
       </c>
       <c r="R20" t="n">
-        <v>6646466</v>
+        <v>6646448</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2641,7 +2638,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2660,10 +2656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462750</v>
+        <v>124461033</v>
       </c>
       <c r="B21" t="n">
-        <v>100279</v>
+        <v>103528</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2672,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2696,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698509</v>
+        <v>698451</v>
       </c>
       <c r="R21" t="n">
-        <v>6646485</v>
+        <v>6646709</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2762,10 +2758,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124474162</v>
+        <v>124457969</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,45 +2770,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698476</v>
+        <v>698343</v>
       </c>
       <c r="R22" t="n">
-        <v>6646591</v>
+        <v>6646433</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2850,29 +2842,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124457802</v>
+        <v>124462736</v>
       </c>
       <c r="B23" t="n">
-        <v>5196</v>
+        <v>110163</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,37 +2876,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698365</v>
+        <v>698509</v>
       </c>
       <c r="R23" t="n">
-        <v>6646448</v>
+        <v>6646485</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2971,10 +2962,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124474165</v>
+        <v>124459239</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2983,41 +2974,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698508</v>
+        <v>698474</v>
       </c>
       <c r="R24" t="n">
-        <v>6646430</v>
+        <v>6646510</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457678</v>
+        <v>124457671</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124457671</v>
+        <v>124457678</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124457969</v>
+        <v>124462736</v>
       </c>
       <c r="B22" t="n">
-        <v>98124</v>
+        <v>110163</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,34 +2774,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698343</v>
+        <v>698509</v>
       </c>
       <c r="R22" t="n">
-        <v>6646433</v>
+        <v>6646485</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462736</v>
+        <v>124457969</v>
       </c>
       <c r="B23" t="n">
-        <v>110163</v>
+        <v>98124</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2876,34 +2876,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698509</v>
+        <v>698343</v>
       </c>
       <c r="R23" t="n">
-        <v>6646485</v>
+        <v>6646433</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457671</v>
+        <v>124457678</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124457678</v>
+        <v>124457671</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124474164</v>
+        <v>124459075</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>30115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,34 +1325,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>200985</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698354</v>
+        <v>698467</v>
       </c>
       <c r="R8" t="n">
-        <v>6646460</v>
+        <v>6646525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,28 +1398,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124459075</v>
+        <v>124474164</v>
       </c>
       <c r="B9" t="n">
-        <v>30115</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,39 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>200985</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698467</v>
+        <v>698354</v>
       </c>
       <c r="R9" t="n">
-        <v>6646525</v>
+        <v>6646460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,19 +1501,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457678</v>
+        <v>124457484</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698365</v>
+        <v>698344</v>
       </c>
       <c r="R2" t="n">
-        <v>6646448</v>
+        <v>6646454</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124457671</v>
+        <v>124457542</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698365</v>
+        <v>698344</v>
       </c>
       <c r="R3" t="n">
-        <v>6646448</v>
+        <v>6646454</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124474156</v>
+        <v>124458289</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,45 +891,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698340</v>
+        <v>698368</v>
       </c>
       <c r="R4" t="n">
-        <v>6646487</v>
+        <v>6646466</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,28 +975,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124462473</v>
+        <v>124457802</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,39 +1010,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698461</v>
+        <v>698365</v>
       </c>
       <c r="R5" t="n">
-        <v>6646553</v>
+        <v>6646448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124462750</v>
+        <v>124457352</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,34 +1112,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698509</v>
+        <v>698343</v>
       </c>
       <c r="R6" t="n">
-        <v>6646485</v>
+        <v>6646433</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124458289</v>
+        <v>124474165</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,53 +1210,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698368</v>
+        <v>698508</v>
       </c>
       <c r="R7" t="n">
-        <v>6646466</v>
+        <v>6646430</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,29 +1282,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124459075</v>
+        <v>124474162</v>
       </c>
       <c r="B8" t="n">
-        <v>30115</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,43 +1312,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>200985</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698467</v>
+        <v>698476</v>
       </c>
       <c r="R8" t="n">
-        <v>6646525</v>
+        <v>6646591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124474164</v>
+        <v>124457671</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698354</v>
+        <v>698365</v>
       </c>
       <c r="R9" t="n">
-        <v>6646460</v>
+        <v>6646448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,22 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124474163</v>
+        <v>124474156</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,42 +1521,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698473</v>
+        <v>698340</v>
       </c>
       <c r="R10" t="n">
-        <v>6646591</v>
+        <v>6646487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1597,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1626,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474168</v>
+        <v>124474163</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,38 +1627,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698409</v>
+        <v>698473</v>
       </c>
       <c r="R11" t="n">
-        <v>6646641</v>
+        <v>6646591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1703,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1728,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462497</v>
+        <v>124474161</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,38 +1734,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698461</v>
+        <v>698368</v>
       </c>
       <c r="R12" t="n">
-        <v>6646553</v>
+        <v>6646487</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,28 +1810,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124457484</v>
+        <v>124474168</v>
       </c>
       <c r="B13" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,34 +1845,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698344</v>
+        <v>698409</v>
       </c>
       <c r="R13" t="n">
-        <v>6646454</v>
+        <v>6646641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,19 +1919,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474165</v>
+        <v>124474166</v>
       </c>
       <c r="B14" t="n">
         <v>100279</v>
@@ -1972,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698508</v>
+        <v>698449</v>
       </c>
       <c r="R14" t="n">
-        <v>6646430</v>
+        <v>6646765</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124474161</v>
+        <v>124462497</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,42 +2045,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698368</v>
+        <v>698461</v>
       </c>
       <c r="R15" t="n">
-        <v>6646487</v>
+        <v>6646553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,29 +2117,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124457352</v>
+        <v>124461033</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>103528</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,16 +2151,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2177,17 +2171,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698343</v>
+        <v>698451</v>
       </c>
       <c r="R16" t="n">
-        <v>6646433</v>
+        <v>6646709</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124457542</v>
+        <v>124457969</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>98124</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2283,13 +2277,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698344</v>
+        <v>698343</v>
       </c>
       <c r="R17" t="n">
-        <v>6646454</v>
+        <v>6646433</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2345,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124474162</v>
+        <v>124457678</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,42 +2351,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698476</v>
+        <v>698365</v>
       </c>
       <c r="R18" t="n">
-        <v>6646591</v>
+        <v>6646448</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,29 +2423,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124474166</v>
+        <v>124474164</v>
       </c>
       <c r="B19" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2468,21 +2457,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2492,10 +2481,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698449</v>
+        <v>698354</v>
       </c>
       <c r="R19" t="n">
-        <v>6646765</v>
+        <v>6646460</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124457802</v>
+        <v>124462473</v>
       </c>
       <c r="B20" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,34 +2559,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698365</v>
+        <v>698461</v>
       </c>
       <c r="R20" t="n">
-        <v>6646448</v>
+        <v>6646553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,10 +2650,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124461033</v>
+        <v>124462736</v>
       </c>
       <c r="B21" t="n">
-        <v>103528</v>
+        <v>110163</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2672,16 +2666,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2696,13 +2690,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698451</v>
+        <v>698509</v>
       </c>
       <c r="R21" t="n">
-        <v>6646709</v>
+        <v>6646485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2758,10 +2752,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462736</v>
+        <v>124459239</v>
       </c>
       <c r="B22" t="n">
-        <v>110163</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2770,38 +2764,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698509</v>
+        <v>698474</v>
       </c>
       <c r="R22" t="n">
-        <v>6646485</v>
+        <v>6646510</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2860,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124457969</v>
+        <v>124459075</v>
       </c>
       <c r="B23" t="n">
-        <v>98124</v>
+        <v>30115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2876,37 +2879,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>200985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698343</v>
+        <v>698467</v>
       </c>
       <c r="R23" t="n">
-        <v>6646433</v>
+        <v>6646525</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2944,6 +2952,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2962,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124459239</v>
+        <v>124462750</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2974,47 +2983,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698474</v>
+        <v>698509</v>
       </c>
       <c r="R24" t="n">
-        <v>6646510</v>
+        <v>6646485</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124457542</v>
+        <v>124457352</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698344</v>
+        <v>698343</v>
       </c>
       <c r="R3" t="n">
-        <v>6646454</v>
+        <v>6646433</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124458289</v>
+        <v>124474163</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -914,30 +914,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698368</v>
+        <v>698473</v>
       </c>
       <c r="R4" t="n">
-        <v>6646466</v>
+        <v>6646591</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124457802</v>
+        <v>124474156</v>
       </c>
       <c r="B5" t="n">
-        <v>5196</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,20 +998,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,16 +1020,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698365</v>
+        <v>698340</v>
       </c>
       <c r="R5" t="n">
-        <v>6646448</v>
+        <v>6646487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124457352</v>
+        <v>124462750</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,34 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698343</v>
+        <v>698509</v>
       </c>
       <c r="R6" t="n">
-        <v>6646433</v>
+        <v>6646485</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1198,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124474165</v>
+        <v>124459075</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>30115</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1214,34 +1210,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698508</v>
+        <v>698467</v>
       </c>
       <c r="R7" t="n">
-        <v>6646430</v>
+        <v>6646525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,28 +1283,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124474162</v>
+        <v>124462736</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>110163</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,45 +1314,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698476</v>
+        <v>698509</v>
       </c>
       <c r="R8" t="n">
-        <v>6646591</v>
+        <v>6646485</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,29 +1386,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124457671</v>
+        <v>124457542</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698365</v>
+        <v>698344</v>
       </c>
       <c r="R9" t="n">
-        <v>6646448</v>
+        <v>6646454</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124474156</v>
+        <v>124462497</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,42 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698340</v>
+        <v>698461</v>
       </c>
       <c r="R10" t="n">
-        <v>6646487</v>
+        <v>6646553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,19 +1596,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474163</v>
+        <v>124474162</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1650,7 +1643,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1659,7 +1652,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698473</v>
+        <v>698476</v>
       </c>
       <c r="R11" t="n">
         <v>6646591</v>
@@ -1722,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124474161</v>
+        <v>124457671</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,42 +1727,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698368</v>
+        <v>698365</v>
       </c>
       <c r="R12" t="n">
-        <v>6646487</v>
+        <v>6646448</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,29 +1799,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124474168</v>
+        <v>124462473</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,34 +1833,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698409</v>
+        <v>698461</v>
       </c>
       <c r="R13" t="n">
-        <v>6646641</v>
+        <v>6646553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,19 +1912,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474166</v>
+        <v>124474165</v>
       </c>
       <c r="B14" t="n">
         <v>100279</v>
@@ -1971,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698449</v>
+        <v>698508</v>
       </c>
       <c r="R14" t="n">
-        <v>6646765</v>
+        <v>6646430</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462497</v>
+        <v>124474161</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,38 +2038,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698461</v>
+        <v>698368</v>
       </c>
       <c r="R15" t="n">
-        <v>6646553</v>
+        <v>6646487</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,28 +2114,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124461033</v>
+        <v>124474168</v>
       </c>
       <c r="B16" t="n">
-        <v>103528</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,34 +2149,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698451</v>
+        <v>698409</v>
       </c>
       <c r="R16" t="n">
-        <v>6646709</v>
+        <v>6646641</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,12 +2223,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2339,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124457678</v>
+        <v>124474166</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,34 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698365</v>
+        <v>698449</v>
       </c>
       <c r="R18" t="n">
-        <v>6646448</v>
+        <v>6646765</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,22 +2427,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124474164</v>
+        <v>124457678</v>
       </c>
       <c r="B19" t="n">
-        <v>105117</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,34 +2455,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698354</v>
+        <v>698365</v>
       </c>
       <c r="R19" t="n">
-        <v>6646460</v>
+        <v>6646448</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,22 +2529,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462473</v>
+        <v>124461033</v>
       </c>
       <c r="B20" t="n">
-        <v>5176</v>
+        <v>103528</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2559,39 +2557,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>222412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698461</v>
+        <v>698451</v>
       </c>
       <c r="R20" t="n">
-        <v>6646553</v>
+        <v>6646709</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2650,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462736</v>
+        <v>124474164</v>
       </c>
       <c r="B21" t="n">
-        <v>110163</v>
+        <v>105117</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2666,37 +2659,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698509</v>
+        <v>698354</v>
       </c>
       <c r="R21" t="n">
-        <v>6646485</v>
+        <v>6646460</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2740,19 +2733,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124459239</v>
+        <v>124458289</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2787,24 +2780,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>101</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698474</v>
+        <v>698368</v>
       </c>
       <c r="R22" t="n">
-        <v>6646510</v>
+        <v>6646466</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2845,6 +2841,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2863,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124459075</v>
+        <v>124457802</v>
       </c>
       <c r="B23" t="n">
-        <v>30115</v>
+        <v>5196</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,39 +2876,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>200985</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698467</v>
+        <v>698365</v>
       </c>
       <c r="R23" t="n">
-        <v>6646525</v>
+        <v>6646448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2952,7 +2944,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2962,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124462750</v>
+        <v>124459239</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2983,38 +2974,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698509</v>
+        <v>698474</v>
       </c>
       <c r="R24" t="n">
-        <v>6646485</v>
+        <v>6646510</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124457484</v>
+        <v>124474161</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698344</v>
+        <v>698368</v>
       </c>
       <c r="R2" t="n">
-        <v>6646454</v>
+        <v>6646487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,28 +763,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124457352</v>
+        <v>124462473</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>5176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698343</v>
+        <v>698461</v>
       </c>
       <c r="R3" t="n">
-        <v>6646433</v>
+        <v>6646553</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124474163</v>
+        <v>124458289</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -914,22 +924,30 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698473</v>
+        <v>698368</v>
       </c>
       <c r="R4" t="n">
-        <v>6646591</v>
+        <v>6646466</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474156</v>
+        <v>124474164</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,42 +1016,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698340</v>
+        <v>698354</v>
       </c>
       <c r="R5" t="n">
-        <v>6646487</v>
+        <v>6646460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124462750</v>
+        <v>124461033</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>103528</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698509</v>
+        <v>698451</v>
       </c>
       <c r="R6" t="n">
-        <v>6646485</v>
+        <v>6646709</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124459075</v>
+        <v>124457542</v>
       </c>
       <c r="B7" t="n">
-        <v>30115</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,39 +1224,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>200985</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698467</v>
+        <v>698344</v>
       </c>
       <c r="R7" t="n">
-        <v>6646525</v>
+        <v>6646454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1292,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124462736</v>
+        <v>124457484</v>
       </c>
       <c r="B8" t="n">
-        <v>110163</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,37 +1326,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698509</v>
+        <v>698344</v>
       </c>
       <c r="R8" t="n">
-        <v>6646485</v>
+        <v>6646454</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,7 +1412,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124457542</v>
+        <v>124462497</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1440,14 +1448,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698344</v>
+        <v>698461</v>
       </c>
       <c r="R9" t="n">
-        <v>6646454</v>
+        <v>6646553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462497</v>
+        <v>124474166</v>
       </c>
       <c r="B10" t="n">
         <v>100279</v>
@@ -1542,14 +1550,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698461</v>
+        <v>698449</v>
       </c>
       <c r="R10" t="n">
-        <v>6646553</v>
+        <v>6646765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,19 +1604,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474162</v>
+        <v>124459239</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1643,22 +1651,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698476</v>
+        <v>698474</v>
       </c>
       <c r="R11" t="n">
-        <v>6646591</v>
+        <v>6646510</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1696,29 +1709,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124457671</v>
+        <v>124474165</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,38 +1739,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698365</v>
+        <v>698508</v>
       </c>
       <c r="R12" t="n">
-        <v>6646448</v>
+        <v>6646430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,22 +1817,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124462473</v>
+        <v>124474162</v>
       </c>
       <c r="B13" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,43 +1841,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698461</v>
+        <v>698476</v>
       </c>
       <c r="R13" t="n">
-        <v>6646553</v>
+        <v>6646591</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,28 +1917,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474165</v>
+        <v>124457671</v>
       </c>
       <c r="B14" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,38 +1948,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698508</v>
+        <v>698365</v>
       </c>
       <c r="R14" t="n">
-        <v>6646430</v>
+        <v>6646448</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,22 +2026,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124474161</v>
+        <v>124474168</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,42 +2050,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698368</v>
+        <v>698409</v>
       </c>
       <c r="R15" t="n">
-        <v>6646487</v>
+        <v>6646641</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,7 +2122,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2133,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124474168</v>
+        <v>124457678</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,34 +2156,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698409</v>
+        <v>698365</v>
       </c>
       <c r="R16" t="n">
-        <v>6646641</v>
+        <v>6646448</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,22 +2230,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124457969</v>
+        <v>124474163</v>
       </c>
       <c r="B17" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,41 +2254,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698343</v>
+        <v>698473</v>
       </c>
       <c r="R17" t="n">
-        <v>6646433</v>
+        <v>6646591</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2319,28 +2330,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124474166</v>
+        <v>124462736</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>110163</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,37 +2365,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698449</v>
+        <v>698509</v>
       </c>
       <c r="R18" t="n">
-        <v>6646765</v>
+        <v>6646485</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2427,22 +2439,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124457678</v>
+        <v>124457802</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>5196</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2467,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2541,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124461033</v>
+        <v>124459075</v>
       </c>
       <c r="B20" t="n">
-        <v>103528</v>
+        <v>30115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,34 +2569,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>200985</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698451</v>
+        <v>698467</v>
       </c>
       <c r="R20" t="n">
-        <v>6646709</v>
+        <v>6646525</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,6 +2642,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2643,10 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124474164</v>
+        <v>124462750</v>
       </c>
       <c r="B21" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,37 +2677,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698354</v>
+        <v>698509</v>
       </c>
       <c r="R21" t="n">
-        <v>6646460</v>
+        <v>6646485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2733,22 +2751,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124458289</v>
+        <v>124457352</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,50 +2775,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698368</v>
+        <v>698343</v>
       </c>
       <c r="R22" t="n">
-        <v>6646466</v>
+        <v>6646433</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2841,7 +2847,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124457802</v>
+        <v>124474156</v>
       </c>
       <c r="B23" t="n">
-        <v>5196</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2872,20 +2877,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2894,16 +2899,20 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698365</v>
+        <v>698340</v>
       </c>
       <c r="R23" t="n">
-        <v>6646448</v>
+        <v>6646487</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,22 +2959,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124459239</v>
+        <v>124457969</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2974,47 +2983,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698474</v>
+        <v>698343</v>
       </c>
       <c r="R24" t="n">
-        <v>6646510</v>
+        <v>6646433</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124474161</v>
+        <v>124474166</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698368</v>
+        <v>698449</v>
       </c>
       <c r="R2" t="n">
-        <v>6646487</v>
+        <v>6646765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124462473</v>
+        <v>124459239</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +789,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698461</v>
+        <v>698474</v>
       </c>
       <c r="R3" t="n">
-        <v>6646553</v>
+        <v>6646510</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124458289</v>
+        <v>124462750</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,50 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698368</v>
+        <v>698509</v>
       </c>
       <c r="R4" t="n">
-        <v>6646466</v>
+        <v>6646485</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,7 +972,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124474164</v>
+        <v>124457352</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,37 +1006,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698354</v>
+        <v>698343</v>
       </c>
       <c r="R5" t="n">
-        <v>6646460</v>
+        <v>6646433</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124461033</v>
+        <v>124457671</v>
       </c>
       <c r="B6" t="n">
-        <v>103528</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,38 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698451</v>
+        <v>698365</v>
       </c>
       <c r="R6" t="n">
-        <v>6646709</v>
+        <v>6646448</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124457542</v>
+        <v>124458289</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,41 +1206,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698344</v>
+        <v>698368</v>
       </c>
       <c r="R7" t="n">
-        <v>6646454</v>
+        <v>6646466</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,6 +1290,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1310,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124457484</v>
+        <v>124474161</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,38 +1321,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698344</v>
+        <v>698368</v>
       </c>
       <c r="R8" t="n">
-        <v>6646454</v>
+        <v>6646487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,28 +1397,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124462497</v>
+        <v>124457678</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,34 +1432,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698461</v>
+        <v>698365</v>
       </c>
       <c r="R9" t="n">
-        <v>6646553</v>
+        <v>6646448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124474166</v>
+        <v>124474156</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,38 +1530,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698449</v>
+        <v>698340</v>
       </c>
       <c r="R10" t="n">
-        <v>6646765</v>
+        <v>6646487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1624,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124459239</v>
+        <v>124474163</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1651,27 +1659,22 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698474</v>
+        <v>698473</v>
       </c>
       <c r="R11" t="n">
-        <v>6646510</v>
+        <v>6646591</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,28 +1712,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124474165</v>
+        <v>124462736</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>110163</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,37 +1747,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698508</v>
+        <v>698509</v>
       </c>
       <c r="R12" t="n">
-        <v>6646430</v>
+        <v>6646485</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,22 +1821,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124474162</v>
+        <v>124474165</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,42 +1845,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698476</v>
+        <v>698508</v>
       </c>
       <c r="R13" t="n">
-        <v>6646591</v>
+        <v>6646430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1936,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124457671</v>
+        <v>124474162</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,38 +1947,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698365</v>
+        <v>698476</v>
       </c>
       <c r="R14" t="n">
-        <v>6646448</v>
+        <v>6646591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,25 +2023,26 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124474168</v>
+        <v>124457542</v>
       </c>
       <c r="B15" t="n">
         <v>100279</v>
@@ -2074,14 +2078,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698409</v>
+        <v>698344</v>
       </c>
       <c r="R15" t="n">
-        <v>6646641</v>
+        <v>6646454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,22 +2132,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124457678</v>
+        <v>124459075</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>30115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2156,34 +2160,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>200985</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698365</v>
+        <v>698467</v>
       </c>
       <c r="R16" t="n">
-        <v>6646448</v>
+        <v>6646525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,6 +2233,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2242,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124474163</v>
+        <v>124457484</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2254,42 +2264,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698473</v>
+        <v>698344</v>
       </c>
       <c r="R17" t="n">
-        <v>6646591</v>
+        <v>6646454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,29 +2336,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124462736</v>
+        <v>124461033</v>
       </c>
       <c r="B18" t="n">
-        <v>110163</v>
+        <v>103528</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,13 +2394,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698509</v>
+        <v>698451</v>
       </c>
       <c r="R18" t="n">
-        <v>6646485</v>
+        <v>6646709</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124457802</v>
+        <v>124462473</v>
       </c>
       <c r="B19" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,34 +2472,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698365</v>
+        <v>698461</v>
       </c>
       <c r="R19" t="n">
-        <v>6646448</v>
+        <v>6646553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124459075</v>
+        <v>124474168</v>
       </c>
       <c r="B20" t="n">
-        <v>30115</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,39 +2579,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>200985</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698467</v>
+        <v>698409</v>
       </c>
       <c r="R20" t="n">
-        <v>6646525</v>
+        <v>6646641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,29 +2647,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462750</v>
+        <v>124457969</v>
       </c>
       <c r="B21" t="n">
-        <v>100279</v>
+        <v>98124</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,34 +2681,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698509</v>
+        <v>698343</v>
       </c>
       <c r="R21" t="n">
-        <v>6646485</v>
+        <v>6646433</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2763,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124457352</v>
+        <v>124457802</v>
       </c>
       <c r="B22" t="n">
-        <v>96979</v>
+        <v>5196</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,21 +2783,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2803,13 +2807,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698343</v>
+        <v>698365</v>
       </c>
       <c r="R22" t="n">
-        <v>6646433</v>
+        <v>6646448</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2865,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124474156</v>
+        <v>124462497</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2877,42 +2881,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698340</v>
+        <v>698461</v>
       </c>
       <c r="R23" t="n">
-        <v>6646487</v>
+        <v>6646553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2959,22 +2959,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124457969</v>
+        <v>124474164</v>
       </c>
       <c r="B24" t="n">
-        <v>98124</v>
+        <v>105117</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,37 +2987,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698343</v>
+        <v>698354</v>
       </c>
       <c r="R24" t="n">
-        <v>6646433</v>
+        <v>6646460</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 13179-2025 artfynd.xlsx
+++ b/artfynd/A 13179-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124474166</v>
+        <v>124462497</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698449</v>
+        <v>698461</v>
       </c>
       <c r="R2" t="n">
-        <v>6646765</v>
+        <v>6646553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124459239</v>
+        <v>124474168</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698474</v>
+        <v>698409</v>
       </c>
       <c r="R3" t="n">
-        <v>6646510</v>
+        <v>6646641</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124462750</v>
+        <v>124462736</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>110163</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124457352</v>
+        <v>124474162</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,41 +993,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698343</v>
+        <v>698476</v>
       </c>
       <c r="R5" t="n">
-        <v>6646433</v>
+        <v>6646591</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,28 +1069,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124457671</v>
+        <v>124474161</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1100,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698365</v>
+        <v>698368</v>
       </c>
       <c r="R6" t="n">
-        <v>6646448</v>
+        <v>6646487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,25 +1176,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124458289</v>
+        <v>124474163</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1229,30 +1230,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698368</v>
+        <v>698473</v>
       </c>
       <c r="R7" t="n">
-        <v>6646466</v>
+        <v>6646591</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124474161</v>
+        <v>124457542</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,42 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698368</v>
+        <v>698344</v>
       </c>
       <c r="R8" t="n">
-        <v>6646487</v>
+        <v>6646454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,29 +1386,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124457678</v>
+        <v>124474164</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,34 +1420,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698365</v>
+        <v>698354</v>
       </c>
       <c r="R9" t="n">
-        <v>6646448</v>
+        <v>6646460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124474156</v>
+        <v>124458289</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,45 +1518,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698340</v>
+        <v>698368</v>
       </c>
       <c r="R10" t="n">
-        <v>6646487</v>
+        <v>6646466</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,28 +1602,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124474163</v>
+        <v>124457678</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,42 +1633,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698473</v>
+        <v>698365</v>
       </c>
       <c r="R11" t="n">
-        <v>6646591</v>
+        <v>6646448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,29 +1705,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462736</v>
+        <v>124457802</v>
       </c>
       <c r="B12" t="n">
-        <v>110163</v>
+        <v>5196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,37 +1739,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698509</v>
+        <v>698365</v>
       </c>
       <c r="R12" t="n">
-        <v>6646485</v>
+        <v>6646448</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,7 +1825,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124474165</v>
+        <v>124474166</v>
       </c>
       <c r="B13" t="n">
         <v>100279</v>
@@ -1873,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698508</v>
+        <v>698449</v>
       </c>
       <c r="R13" t="n">
-        <v>6646430</v>
+        <v>6646765</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124474162</v>
+        <v>124474156</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,42 +1939,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698476</v>
+        <v>698340</v>
       </c>
       <c r="R14" t="n">
-        <v>6646591</v>
+        <v>6646487</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2015,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2042,7 +2033,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124457542</v>
+        <v>124462750</v>
       </c>
       <c r="B15" t="n">
         <v>100279</v>
@@ -2078,17 +2069,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698344</v>
+        <v>698509</v>
       </c>
       <c r="R15" t="n">
-        <v>6646454</v>
+        <v>6646485</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2144,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124459075</v>
+        <v>124459239</v>
       </c>
       <c r="B16" t="n">
-        <v>30115</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2156,46 +2147,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>200985</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698467</v>
+        <v>698474</v>
       </c>
       <c r="R16" t="n">
-        <v>6646525</v>
+        <v>6646510</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2233,7 +2228,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2354,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124461033</v>
+        <v>124459075</v>
       </c>
       <c r="B18" t="n">
-        <v>103528</v>
+        <v>30115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,34 +2364,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>200985</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698451</v>
+        <v>698467</v>
       </c>
       <c r="R18" t="n">
-        <v>6646709</v>
+        <v>6646525</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,6 +2437,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462473</v>
+        <v>124457969</v>
       </c>
       <c r="B19" t="n">
-        <v>5176</v>
+        <v>98124</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,42 +2472,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698461</v>
+        <v>698343</v>
       </c>
       <c r="R19" t="n">
-        <v>6646553</v>
+        <v>6646433</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2563,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124474168</v>
+        <v>124462473</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,34 +2574,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698409</v>
+        <v>698461</v>
       </c>
       <c r="R20" t="n">
-        <v>6646641</v>
+        <v>6646553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,22 +2653,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124457969</v>
+        <v>124474165</v>
       </c>
       <c r="B21" t="n">
-        <v>98124</v>
+        <v>100279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2681,37 +2681,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698343</v>
+        <v>698508</v>
       </c>
       <c r="R21" t="n">
-        <v>6646433</v>
+        <v>6646430</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2755,22 +2755,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124457802</v>
+        <v>124461033</v>
       </c>
       <c r="B22" t="n">
-        <v>5196</v>
+        <v>103528</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,34 +2783,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skräddarkärret, Upl</t>
+          <t>Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698365</v>
+        <v>698451</v>
       </c>
       <c r="R22" t="n">
-        <v>6646448</v>
+        <v>6646709</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462497</v>
+        <v>124457352</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,37 +2885,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storkärret, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698461</v>
+        <v>698343</v>
       </c>
       <c r="R23" t="n">
-        <v>6646553</v>
+        <v>6646433</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124474164</v>
+        <v>124457671</v>
       </c>
       <c r="B24" t="n">
-        <v>105117</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2983,38 +2983,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vagn, Upl</t>
+          <t>Skräddarkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698354</v>
+        <v>698365</v>
       </c>
       <c r="R24" t="n">
-        <v>6646460</v>
+        <v>6646448</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
